--- a/InputData/trans/EoDfVUwFC/Elast of Demand for Veh Use wrt Fuel Cost.xlsx
+++ b/InputData/trans/EoDfVUwFC/Elast of Demand for Veh Use wrt Fuel Cost.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28521"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\EoDfVUwFC\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8285D13AD5323FA0B9898A18B47B5F15BED2B31A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13935"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -18,59 +19,150 @@
     <sheet name="Rail and Ships" sheetId="3" r:id="rId4"/>
     <sheet name="EoDfVUwFC" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
   <si>
+    <t>EoDfVUwFC Elasticity of Demand for Vehicle Use wrt Fuel Cost</t>
+  </si>
+  <si>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>LDVs</t>
+  </si>
+  <si>
+    <t>U.S. EPA and U.S. NHTSA</t>
+  </si>
+  <si>
+    <t>2017 and Later Model Year Light-Duty Vehicle Greenhouse Gas Emissions and Corporate Average Fuel Economy Standards (Final Rule)</t>
+  </si>
+  <si>
+    <t>http://www.gpo.gov/fdsys/pkg/FR-2012-10-15/pdf/2012-21972.pdf</t>
+  </si>
+  <si>
+    <t>Page 62716, second column, first bullet point, second sentence</t>
+  </si>
+  <si>
+    <t>HDVs</t>
+  </si>
+  <si>
+    <t>U.S. EPA and NHTSA</t>
+  </si>
+  <si>
+    <t>Greenhouse Gas Emissions Standards and Fuel Efficiency Standards for Medium- and Heavy-Duty Engines and Vehicles (Final Rule)</t>
+  </si>
+  <si>
+    <t>http://www.gpo.gov/fdsys/pkg/FR-2011-09-15/pdf/2011-20740.pdf</t>
+  </si>
+  <si>
+    <t>Page 57329, first column, last sentence</t>
+  </si>
+  <si>
+    <t>aircraft: fraction of airfare costs attributable to fuel</t>
+  </si>
+  <si>
+    <t>International Air Transportation Association</t>
+  </si>
+  <si>
+    <t>IATA Economic Briefing: Airline Fuel and Labour Cost Share</t>
+  </si>
+  <si>
+    <t>http://www.iata.org/whatwedo/Documents/economics/Airline_Labour_Cost_Share_Feb2010.pdf</t>
+  </si>
+  <si>
+    <t>First paragraph</t>
+  </si>
+  <si>
+    <t>aircraft: elasticity of demand for air travel</t>
+  </si>
+  <si>
+    <t>Air Travel Demand: IATA Economics Briefing No 9</t>
+  </si>
+  <si>
+    <t>http://www.iata.org/whatwedo/Documents/economics/air_travel_demand.pdf</t>
+  </si>
+  <si>
+    <t>Page 7, "National Level"</t>
+  </si>
+  <si>
+    <t>rail</t>
+  </si>
+  <si>
+    <t>Sinha, Kumares and Samuel Labi</t>
+  </si>
+  <si>
+    <t>Transportation Decision Making: Principles of Project Evaluation and Programming</t>
+  </si>
+  <si>
+    <t>http://books.google.com/books?id=870LEFbxZTQC&amp;pg=PA54</t>
+  </si>
+  <si>
+    <t>Page 54, Table 3.4</t>
+  </si>
+  <si>
+    <t>ships</t>
+  </si>
+  <si>
+    <t>motorbikes</t>
+  </si>
+  <si>
+    <t>Assumed to be the same as LDVs</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>This variable is also known as the "Fuel Economy Rebound Effect" or "Fuel Cost Rebound Effect." It is the change</t>
+  </si>
+  <si>
+    <t>in VMT as a fraction of the change in fuel cost. E.g. for a 1% increase in fuel cost per mile, VMT changes by -0.1%.</t>
+  </si>
+  <si>
+    <t>LDV and HDV elasticities are taken from two separate analyses, each done jointly</t>
+  </si>
+  <si>
+    <t>by the EPA and NHTSA.  They considered certain ranges of values and selected a</t>
+  </si>
+  <si>
+    <t>final elasticity value for use in their analysis (supporting their rulemaking).</t>
+  </si>
+  <si>
+    <t>We use the value they selected.</t>
+  </si>
+  <si>
+    <t>Aircraft</t>
+  </si>
+  <si>
+    <t>Fraction of airfare cost attributable to fuel:</t>
+  </si>
+  <si>
     <t>Elasticity of Demand for Air Travel WRT to Price</t>
   </si>
   <si>
     <t>Elasticity of Demand for Air Travel WRT to Fuel Price</t>
   </si>
   <si>
-    <t>Sources:</t>
-  </si>
-  <si>
-    <t>LDVs</t>
-  </si>
-  <si>
-    <t>HDVs</t>
-  </si>
-  <si>
-    <t>aircraft: fraction of airfare costs attributable to fuel</t>
-  </si>
-  <si>
-    <t>International Air Transportation Association</t>
-  </si>
-  <si>
-    <t>IATA Economic Briefing: Airline Fuel and Labour Cost Share</t>
-  </si>
-  <si>
-    <t>http://www.iata.org/whatwedo/Documents/economics/Airline_Labour_Cost_Share_Feb2010.pdf</t>
-  </si>
-  <si>
-    <t>First paragraph</t>
-  </si>
-  <si>
-    <t>Aircraft</t>
-  </si>
-  <si>
-    <t>Fraction of airfare cost attributable to fuel:</t>
-  </si>
-  <si>
-    <t>aircraft: elasticity of demand for air travel</t>
-  </si>
-  <si>
-    <t>Air Travel Demand: IATA Economics Briefing No 9</t>
-  </si>
-  <si>
-    <t>http://www.iata.org/whatwedo/Documents/economics/air_travel_demand.pdf</t>
-  </si>
-  <si>
-    <t>Page 7, "National Level"</t>
+    <t>Note: We only have data on passenger air travel elasticities, not air freight.  We therefore</t>
   </si>
   <si>
     <t>assume demand for freight air has a similar elasticity to the demand for passenger air</t>
@@ -88,9 +180,6 @@
     <t>a digital version of the product.)</t>
   </si>
   <si>
-    <t>Note: We only have data on passenger air travel elasticities, not air freight.  We therefore</t>
-  </si>
-  <si>
     <t>This sheet contains the data from Table 3.4 of Sinha and Labi's</t>
   </si>
   <si>
@@ -100,164 +189,92 @@
     <t>access the data here than in the printed book.</t>
   </si>
   <si>
+    <t>Table 3.4 - Estimated Fuel Price Elasticities by Mode and Fuel Type</t>
+  </si>
+  <si>
+    <t>Short-Run Elasticity</t>
+  </si>
+  <si>
+    <t>Long-Run Elasticity</t>
+  </si>
+  <si>
     <t>Mode</t>
   </si>
   <si>
     <t>Fuel Type</t>
   </si>
   <si>
-    <t>Short-Run Elasticity</t>
-  </si>
-  <si>
     <t>Low Est.</t>
   </si>
   <si>
     <t>High Est.</t>
   </si>
   <si>
-    <t>Long-Run Elasticity</t>
-  </si>
-  <si>
     <t>Road</t>
   </si>
   <si>
+    <t>gasoline</t>
+  </si>
+  <si>
+    <t>diesel (truck)</t>
+  </si>
+  <si>
+    <t>diesel (bus)</t>
+  </si>
+  <si>
+    <t>propane</t>
+  </si>
+  <si>
+    <t>CNG</t>
+  </si>
+  <si>
     <t>Rail</t>
   </si>
   <si>
+    <t>diesel</t>
+  </si>
+  <si>
     <t>Aviation</t>
   </si>
   <si>
+    <t>turbo</t>
+  </si>
+  <si>
     <t>Marine</t>
   </si>
   <si>
-    <t>gasoline</t>
-  </si>
-  <si>
-    <t>diesel (bus)</t>
-  </si>
-  <si>
-    <t>diesel (truck)</t>
-  </si>
-  <si>
-    <t>propane</t>
-  </si>
-  <si>
-    <t>CNG</t>
-  </si>
-  <si>
-    <t>diesel</t>
-  </si>
-  <si>
-    <t>turbo</t>
-  </si>
-  <si>
     <t>Sources: Halger Bailly (1999), VTPI (2006)</t>
   </si>
   <si>
-    <t>Table 3.4 - Estimated Fuel Price Elasticities by Mode and Fuel Type</t>
-  </si>
-  <si>
-    <t>rail</t>
-  </si>
-  <si>
-    <t>Sinha, Kumares and Samuel Labi</t>
-  </si>
-  <si>
-    <t>Page 54, Table 3.4</t>
-  </si>
-  <si>
-    <t>http://books.google.com/books?id=870LEFbxZTQC&amp;pg=PA54</t>
-  </si>
-  <si>
-    <t>ships</t>
-  </si>
-  <si>
     <t>Elasticities Selected for Use in Model</t>
   </si>
   <si>
     <t>Ships</t>
   </si>
   <si>
+    <t>We use the average of the middle two elasticity values (the short-run high estimate and the long-run low estimate),</t>
+  </si>
+  <si>
     <t>primarily (A) to avoid outliers, which the short-run low and long-run high estimates sometimes seem to be, and</t>
   </si>
   <si>
     <t>(B) because this results in elasticities more in line with those found for HDVs in the U.S. study.</t>
   </si>
   <si>
-    <t>We use the average of the middle two elasticity values (the short-run high estimate and the long-run low estimate),</t>
-  </si>
-  <si>
-    <t>U.S. EPA and U.S. NHTSA</t>
-  </si>
-  <si>
-    <t>2017 and Later Model Year Light-Duty Vehicle Greenhouse Gas Emissions and Corporate Average Fuel Economy Standards (Final Rule)</t>
-  </si>
-  <si>
-    <t>http://www.gpo.gov/fdsys/pkg/FR-2012-10-15/pdf/2012-21972.pdf</t>
-  </si>
-  <si>
-    <t>U.S. EPA and NHTSA</t>
-  </si>
-  <si>
-    <t>Greenhouse Gas Emissions Standards and Fuel Efficiency Standards for Medium- and Heavy-Duty Engines and Vehicles (Final Rule)</t>
-  </si>
-  <si>
-    <t>http://www.gpo.gov/fdsys/pkg/FR-2011-09-15/pdf/2011-20740.pdf</t>
-  </si>
-  <si>
-    <t>LDV and HDV elasticities are taken from two separate analyses, each done jointly</t>
-  </si>
-  <si>
-    <t>by the EPA and NHTSA.  They considered certain ranges of values and selected a</t>
-  </si>
-  <si>
-    <t>final elasticity value for use in their analysis (supporting their rulemaking).</t>
-  </si>
-  <si>
-    <t>We use the value they selected.</t>
-  </si>
-  <si>
-    <t>Page 62716, second column, first bullet point, second sentence</t>
-  </si>
-  <si>
-    <t>Page 57329, first column, last sentence</t>
-  </si>
-  <si>
-    <t>Transportation Decision Making: Principles of Project Evaluation and Programming</t>
-  </si>
-  <si>
-    <t>motorbikes</t>
-  </si>
-  <si>
-    <t>Assumed to be the same as LDVs</t>
-  </si>
-  <si>
-    <t>EoDfVUwFC Elasticity of Demand for Vehicle Use wrt Fuel Cost</t>
-  </si>
-  <si>
     <t>Vehicle</t>
   </si>
   <si>
+    <t>Elasticity (dimensionless)</t>
+  </si>
+  <si>
     <t>aircraft</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This variable is also known as the "Fuel Economy Rebound Effect" or "Fuel Cost Rebound Effect." It is the change</t>
-  </si>
-  <si>
-    <t>in VMT as a fraction of the change in fuel cost. E.g. for a 1% increase in fuel cost per mile, VMT changes by -0.1%.</t>
-  </si>
-  <si>
-    <t>Elasticity (dimensionless)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,7 +332,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -325,18 +342,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -618,234 +632,234 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" s="2">
         <v>2012</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="B10" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="2">
         <v>2011</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
       <c r="B17" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
       <c r="B19" s="2">
         <v>2010</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
       <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
       <c r="B24" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
       <c r="B26" s="2">
         <v>2008</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
       <c r="B28" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
       <c r="B31" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="B33" s="2">
         <v>2007</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="B34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="B35" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="B36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="B38" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="B39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="B40" s="2">
         <v>2007</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="B41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="B42" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="B43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="B45" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="B46" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B21" r:id="rId1"/>
-    <hyperlink ref="B28" r:id="rId2"/>
-    <hyperlink ref="B35" r:id="rId3"/>
-    <hyperlink ref="B42" r:id="rId4"/>
-    <hyperlink ref="B14" r:id="rId5"/>
-    <hyperlink ref="B7" r:id="rId6"/>
+    <hyperlink ref="B21" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B28" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B35" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B42" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId7"/>
@@ -853,41 +867,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5">
         <v>-0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7" s="5">
         <v>-0.15</v>
@@ -900,73 +914,73 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="11" max="11" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>0.36699999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>-0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="B7" s="5">
         <f>B5*B3</f>
         <v>-0.29360000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -975,31 +989,31 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -1007,42 +1021,42 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="C6" s="10" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2">
         <v>-0.1</v>
@@ -1057,12 +1071,12 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C9" s="2">
         <v>-0.05</v>
@@ -1077,12 +1091,12 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2">
         <v>-0.05</v>
@@ -1097,12 +1111,12 @@
         <v>-0.45</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2">
         <v>-0.1</v>
@@ -1117,12 +1131,12 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>-0.1</v>
@@ -1137,12 +1151,12 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C13" s="2">
         <v>-0.05</v>
@@ -1157,12 +1171,12 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C14" s="2">
         <v>-0.05</v>
@@ -1177,12 +1191,12 @@
         <v>-0.45</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C15" s="2">
         <v>-0.1</v>
@@ -1197,12 +1211,12 @@
         <v>-0.45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2">
         <v>-0.02</v>
@@ -1217,47 +1231,47 @@
         <v>-0.45</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B22" s="5">
         <f>AVERAGE(D13:E13)</f>
         <v>-0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B23" s="5">
         <f>AVERAGE(D16:E16)</f>
         <v>-0.15000000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1273,75 +1287,75 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30">
       <c r="A1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="9">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8">
         <f>'LDVs and HDVs'!B6</f>
         <v>-0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <f>'LDVs and HDVs'!B7</f>
         <v>-0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="9">
+        <v>75</v>
+      </c>
+      <c r="B4" s="8">
         <f>Aircraft!B7</f>
         <v>-0.29360000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <f>'Rail and Ships'!B22</f>
         <v>-0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <f>'Rail and Ships'!B23</f>
         <v>-0.15000000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="9">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
         <f>B2</f>
         <v>-0.1</v>
       </c>
@@ -1350,4 +1364,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27B330F4-4B7E-4B75-9D50-D87462778400}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4772CC5D-72EE-4BD4-B7E1-8F0B3C599B70}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE76C3D0-78FF-4BAF-A34C-10EF37202BA6}"/>
 </file>